--- a/pathway_pipeline_v2/iembase-diseases-with-pathbank-pathways-and-hmdb-codes.xlsx
+++ b/pathway_pipeline_v2/iembase-diseases-with-pathbank-pathways-and-hmdb-codes.xlsx
@@ -11,7 +11,7 @@
     <sheet name="IEMbase_Diseases_with_Abbreviat" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">IEMbase_Diseases_with_Abbreviat!$A$1:$D$91</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">IEMbase_Diseases_with_Abbreviat!$A$1:$D$92</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="550">
   <si>
     <t xml:space="preserve">Disease</t>
   </si>
@@ -899,6 +899,24 @@
   </si>
   <si>
     <t xml:space="preserve">Glutaric acid (HMDB0000661); Glutarylcarnitine (HMDB0013130); 3-Hydroxyglutaric acid (HMDB0000428)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYCTK-related D-glycerate kinase deficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYCTK-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glyceric acid ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Glyceric Aciduria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMP0000529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glyceric acid (HMDB0000139)</t>
   </si>
   <si>
     <t xml:space="preserve">Guanidinoacetate methyltransferase deficiency</t>
@@ -1664,7 +1682,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1709,6 +1727,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1752,7 +1776,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1783,6 +1807,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1929,7 +1957,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51"/>
@@ -3041,100 +3069,100 @@
       <c r="A51" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="2" t="n">
+        <v>610516</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>300322</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>321</v>
@@ -3157,7 +3185,7 @@
         <v>326</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>243500</v>
+        <v>300322</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>327</v>
@@ -3180,7 +3208,7 @@
         <v>332</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>609016</v>
+        <v>243500</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>333</v>
@@ -3203,7 +3231,7 @@
         <v>338</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>143450</v>
+        <v>609016</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>339</v>
@@ -3226,7 +3254,7 @@
         <v>344</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>222700</v>
+        <v>143450</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>345</v>
@@ -3249,7 +3277,7 @@
         <v>350</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>248360</v>
+        <v>222700</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>351</v>
@@ -3272,7 +3300,7 @@
         <v>356</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>248600</v>
+        <v>248360</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>357</v>
@@ -3295,7 +3323,7 @@
         <v>362</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>201450</v>
+        <v>248600</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>363</v>
@@ -3318,7 +3346,7 @@
         <v>368</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>250850</v>
+        <v>201450</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>369</v>
@@ -3341,7 +3369,7 @@
         <v>374</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>251000</v>
+        <v>250850</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>375</v>
@@ -3364,7 +3392,7 @@
         <v>380</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>260920</v>
+        <v>251000</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>381</v>
@@ -3386,40 +3414,40 @@
       <c r="A66" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="2" t="n">
+        <v>260920</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>36</v>
+      <c r="F66" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>252450</v>
+        <v>392</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>395</v>
+        <v>36</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>396</v>
@@ -3430,7 +3458,7 @@
         <v>397</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>611412</v>
+        <v>252450</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>398</v>
@@ -3439,81 +3467,81 @@
         <v>399</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>36</v>
+        <v>400</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>611412</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>300872</v>
+        <v>407</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>300872</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D71" s="1" t="s">
         <v>413</v>
       </c>
+      <c r="D71" s="6" t="s">
+        <v>414</v>
+      </c>
       <c r="E71" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F71" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>258870</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>418</v>
@@ -3531,12 +3559,12 @@
         <v>422</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>423</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>311250</v>
+        <v>258870</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>424</v>
@@ -3554,12 +3582,12 @@
         <v>428</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>429</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>261600</v>
+        <v>311250</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>430</v>
@@ -3577,12 +3605,12 @@
         <v>434</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>435</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>170100</v>
+        <v>261600</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>436</v>
@@ -3604,31 +3632,31 @@
       <c r="A76" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="2" t="n">
+        <v>170100</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>606054</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>449</v>
@@ -3651,7 +3679,7 @@
         <v>454</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>266500</v>
+        <v>606054</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>455</v>
@@ -3674,7 +3702,7 @@
         <v>460</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>614707</v>
+        <v>266500</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>461</v>
@@ -3683,73 +3711,73 @@
         <v>462</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>463</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>614707</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="F80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>36</v>
+      <c r="F81" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>201470</v>
+        <v>477</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>480</v>
+        <v>36</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>481</v>
@@ -3760,7 +3788,7 @@
         <v>482</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>600737</v>
+        <v>201470</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>483</v>
@@ -3783,7 +3811,7 @@
         <v>488</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>212140</v>
+        <v>600737</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>489</v>
@@ -3792,50 +3820,50 @@
         <v>490</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>36</v>
+        <v>491</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>492</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>184420</v>
+        <v>212140</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>271980</v>
+        <v>184420</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>501</v>
@@ -3846,7 +3874,7 @@
         <v>502</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>606003</v>
+        <v>271980</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>503</v>
@@ -3866,42 +3894,42 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>406</v>
+        <v>508</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>300872</v>
+        <v>606003</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>407</v>
+        <v>509</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>406</v>
+        <v>510</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>511</v>
+        <v>412</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>276700</v>
+        <v>300872</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>512</v>
+        <v>413</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="E89" s="1" t="s">
         <v>514</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>412</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>515</v>
@@ -3915,7 +3943,7 @@
         <v>517</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>258900</v>
+        <v>276700</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>518</v>
@@ -3938,12 +3966,12 @@
         <v>523</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>201475</v>
+        <v>258900</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -3952,7 +3980,7 @@
       <c r="F91" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="1" t="s">
         <v>528</v>
       </c>
     </row>
@@ -3961,12 +3989,12 @@
         <v>529</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>603592</v>
+        <v>201475</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="5" t="s">
         <v>531</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -3975,16 +4003,16 @@
       <c r="F92" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="G92" s="5" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>535</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>234580</v>
+        <v>603592</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>536</v>
@@ -4002,24 +4030,46 @@
         <v>540</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+    <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
         <v>541</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>234580</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D91"/>
+  <autoFilter ref="A1:D92"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="236792; 600721"/>
   </hyperlinks>
